--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>616</v>
+        <v>125</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>309</v>
+        <v>73</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1674</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 164 active clubs (of 174 total).</t>
+          <t>Across 160 active clubs (of 179 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -676,26 +676,26 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Division D</t>
+          <t>Division F</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -704,23 +704,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Division F</t>
+          <t>Division D</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>216</v>
+        <v>44</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -788,23 +788,23 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>19</v>
@@ -816,26 +816,26 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>179</v>
+        <v>24</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -844,26 +844,26 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Division B</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -872,26 +872,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division G</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -900,26 +900,26 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Division G</t>
+          <t>Division B</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>20</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1151,19 +1151,19 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="H29" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1721,19 +1721,19 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="37">
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2102,28 +2102,28 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2132,898 +2132,898 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3032,28 +3032,28 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3092,58 +3092,58 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3152,538 +3152,538 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Celestial Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -3722,28 +3722,28 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -3752,199 +3752,199 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F104" s="8" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3962,28 +3962,28 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3992,46 +3992,46 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>0</v>
@@ -4040,181 +4040,181 @@
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
@@ -4223,28 +4223,28 @@
         <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>0</v>
@@ -4253,238 +4253,238 @@
         <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>CSI Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Chilaw Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Eravur Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" s="8" t="n">
         <v>0</v>
@@ -4493,28 +4493,28 @@
         <v>0</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
@@ -4523,115 +4523,115 @@
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>0</v>
@@ -4643,148 +4643,148 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>IDL Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>0</v>
@@ -4793,25 +4793,25 @@
         <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Kekirawa Toastmasters</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>0</v>
@@ -4823,46 +4823,46 @@
         <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>0</v>
@@ -4913,21 +4913,21 @@
         <v>0</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
@@ -4937,34 +4937,34 @@
         <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -4973,16 +4973,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -4994,90 +4994,90 @@
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
@@ -5087,31 +5087,31 @@
         <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Panadura Bar Association Toastmasters</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5120,24 +5120,24 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5147,27 +5147,27 @@
         <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5177,27 +5177,27 @@
         <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
@@ -5210,28 +5210,28 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" s="6" t="n">
         <v>0</v>
@@ -5243,25 +5243,25 @@
         <v>0</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>0</v>
@@ -5273,21 +5273,21 @@
         <v>0</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5300,24 +5300,24 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5330,28 +5330,28 @@
         <v>0</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5363,21 +5363,21 @@
         <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,11 +5578,11 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>IESL Kandurata Chapter Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,16 +5668,16 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5698,16 +5698,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Wennappuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5728,16 +5728,16 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5758,16 +5758,16 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
@@ -5788,16 +5788,16 @@
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D166" s="8" t="n">
@@ -5813,126 +5813,6 @@
         <v>0</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>TalkCrafters Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>Union Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>E-04</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Wennappuwa Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5947,10 +5827,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5973,7 +5853,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6018,662 +5898,14 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Silvermill Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>NHCO Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Startup Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>APIIT Kandy Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Awakening Toastmasters</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>C-01</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Ceylinco Life Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>HNB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Horana Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Kandy Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>PIM Toastmasters</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Panadura Toastmasters</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Rajagiriya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Braybrooke Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Smedley Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>CIPM Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Capital Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Central Link Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Dowels Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>HSBC Global Service Centre</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Ja-Ela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Kadawatha Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Kelaniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Matale Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Moratuwa Toastmasters</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>The Millennium Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -6690,10 +5922,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6716,7 +5948,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6752,12 +5984,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -6770,16 +6002,16 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -6797,7 +6029,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -6806,815 +6038,23 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>hSenid Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kandy Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>AATSL Emerging Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>IESL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Matara Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Tiqri Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Torrington Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Wednesday 7 Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>B-03</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>AATSL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Aitken Spence Toastmasters</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Anuradhapura Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>G-03</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>BOI Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>A-04</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Bcis Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>CSE Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>A-04</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Commercial Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Dehiwala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Dialog Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Expolanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>GTN Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>IFS Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Kaduwela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Kegalle Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Marketers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>NTG Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Nations Toastmasters</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Oasis Toastmasters</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Peradeniya University Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Sampath Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Siyane Toastmasters</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>The Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>UOC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Voice Your Dream Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>CBL Foods Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CBA Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Central Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Readers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
         <v>125</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>63</v>
@@ -566,7 +566,7 @@
         <v>73</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>261</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>18</v>
@@ -692,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>19</v>
@@ -711,7 +711,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>7</v>
@@ -720,7 +720,7 @@
         <v>18</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -739,7 +739,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9</v>
@@ -748,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>14</v>
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -816,23 +816,23 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>19</v>
@@ -844,23 +844,23 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>19</v>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>4</v>
@@ -888,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>18</v>
@@ -907,7 +907,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>17</v>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>3</v>
@@ -1043,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1064,7 +1064,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>2</v>
@@ -1073,7 +1073,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1247,13 +1247,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1487,13 +1487,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1532,19 +1532,19 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1664,7 +1664,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>1</v>
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1712,19 +1712,19 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1772,16 +1772,16 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>1</v>
@@ -1823,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1952,25 +1952,25 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>3</v>
@@ -1982,25 +1982,25 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>3</v>
@@ -2012,25 +2012,25 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>3</v>
@@ -2042,25 +2042,25 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>3</v>
@@ -2072,19 +2072,19 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>1</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2102,28 +2102,28 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2132,16 +2132,16 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>0</v>
@@ -2153,21 +2153,21 @@
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -2177,27 +2177,27 @@
         <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
@@ -2210,28 +2210,28 @@
         <v>0</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>0</v>
@@ -2240,24 +2240,24 @@
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
@@ -2267,37 +2267,37 @@
         <v>0</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -2308,29 +2308,29 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>2</v>
@@ -2338,20 +2338,20 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>2</v>
@@ -2368,23 +2368,23 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>0</v>
@@ -2398,26 +2398,26 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -2428,16 +2428,16 @@
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>2</v>
@@ -2458,20 +2458,20 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>2</v>
@@ -2488,26 +2488,26 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="8" t="n">
         <v>0</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
@@ -2548,26 +2548,26 @@
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>0</v>
@@ -2578,26 +2578,26 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>0</v>
@@ -2608,29 +2608,29 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>2</v>
@@ -2638,16 +2638,16 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -2668,20 +2668,20 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>2</v>
@@ -2698,16 +2698,16 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>2</v>
@@ -2728,16 +2728,16 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>2</v>
@@ -2758,16 +2758,16 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2777,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>2</v>
@@ -2788,26 +2788,26 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>1</v>
@@ -2818,29 +2818,29 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>2</v>
@@ -2848,26 +2848,26 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="8" t="n">
         <v>0</v>
@@ -2878,26 +2878,26 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>0</v>
@@ -2908,29 +2908,29 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>2</v>
@@ -2942,22 +2942,22 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="6" t="n">
         <v>0</v>
@@ -2968,16 +2968,16 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -2987,121 +2987,121 @@
         <v>0</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="8" t="n">
         <v>0</v>
@@ -3110,40 +3110,40 @@
         <v>0</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -3182,16 +3182,16 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -3272,16 +3272,16 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="n">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
         <v>1</v>
@@ -3298,26 +3298,26 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>0</v>
@@ -3328,16 +3328,16 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
@@ -3347,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="8" t="n">
         <v>1</v>
@@ -3358,26 +3358,26 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>0</v>
@@ -3388,20 +3388,20 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="8" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
         <v>1</v>
@@ -3418,29 +3418,29 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>1</v>
@@ -3448,16 +3448,16 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Celestial Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
@@ -3478,16 +3478,16 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
@@ -3602,16 +3602,16 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>1</v>
@@ -3632,16 +3632,16 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="8" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
         <v>1</v>
@@ -3658,26 +3658,26 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Celestial Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>0</v>
@@ -3688,16 +3688,16 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
@@ -3718,20 +3718,20 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>1</v>
@@ -3748,16 +3748,16 @@
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
@@ -3767,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
         <v>1</v>
@@ -3778,26 +3778,26 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>0</v>
@@ -3808,20 +3808,20 @@
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
         <v>1</v>
@@ -3838,16 +3838,16 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
@@ -3868,29 +3868,29 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="8" t="n">
         <v>1</v>
@@ -3898,26 +3898,26 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
         <v>0</v>
@@ -3928,20 +3928,20 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
         <v>1</v>
@@ -3958,16 +3958,16 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
@@ -3980,28 +3980,28 @@
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>0</v>
@@ -4013,21 +4013,21 @@
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
@@ -4048,16 +4048,16 @@
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
@@ -4078,16 +4078,16 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
@@ -4108,16 +4108,16 @@
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
@@ -4138,16 +4138,16 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
@@ -4168,16 +4168,16 @@
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
@@ -4198,16 +4198,16 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4228,16 +4228,16 @@
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
@@ -4258,16 +4258,16 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
@@ -4288,16 +4288,16 @@
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>CSI Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
@@ -4318,16 +4318,16 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
@@ -4348,16 +4348,16 @@
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>CSI Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
@@ -4378,16 +4378,16 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Chilaw Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
@@ -4408,16 +4408,16 @@
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
@@ -4438,16 +4438,16 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Chilaw Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
@@ -4468,16 +4468,16 @@
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Eravur Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
@@ -4498,16 +4498,16 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
@@ -4528,16 +4528,16 @@
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Eravur Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
@@ -4558,16 +4558,16 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
@@ -4588,16 +4588,16 @@
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
@@ -4618,16 +4618,16 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
@@ -4648,16 +4648,16 @@
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
@@ -4678,16 +4678,16 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -4708,16 +4708,16 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
@@ -4738,16 +4738,16 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>IDL Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
@@ -4768,16 +4768,16 @@
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
@@ -4798,16 +4798,16 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Kekirawa Toastmasters</t>
+          <t>IDL Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
@@ -4828,16 +4828,16 @@
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
@@ -4858,16 +4858,16 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Kekirawa Toastmasters</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
@@ -4888,16 +4888,16 @@
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4918,16 +4918,16 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
@@ -4948,16 +4948,16 @@
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
@@ -4978,16 +4978,16 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
@@ -5008,16 +5008,16 @@
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
@@ -5038,16 +5038,16 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5068,16 +5068,16 @@
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
@@ -5098,16 +5098,16 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Panadura Bar Association Toastmasters</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
@@ -5128,16 +5128,16 @@
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5158,16 +5158,16 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Panadura Bar Association Toastmasters</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5188,16 +5188,16 @@
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
@@ -5218,16 +5218,16 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,16 +5248,16 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5278,16 +5278,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5308,16 +5308,16 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,16 +5368,16 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Union Bank Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,7 +5668,7 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -491,7 +491,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 160 active clubs (of 179 total).</t>
+          <t>Across 160 active clubs (of 179 total). Level 2 / OMM: from 2026-27, Toastmasters counts Online Meeting Mastery exploration completions toward the same DCP goals as Level 2 and reports them as one number, so the two can't be shown separately.</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -5853,7 +5853,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
